--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488062_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488062_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3049</v>
+        <v>5.0848</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6323</v>
+        <v>4.318</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6726</v>
+        <v>0.7668</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7464</v>
+        <v>3.6929</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1673</v>
+        <v>5.8013</v>
       </c>
       <c r="I2" t="n">
-        <v>0.421</v>
+        <v>-2.1084</v>
       </c>
       <c r="J2" t="n">
-        <v>1.286</v>
+        <v>4.8558</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5777</v>
+        <v>6.0533</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8637</v>
+        <v>-1.1975</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0324</v>
+        <v>-1.1629</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5896</v>
+        <v>-0.252</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4428</v>
+        <v>-0.9109</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7751</v>
+        <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2085</v>
+        <v>0.7378</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5794</v>
+        <v>0.7903</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6291</v>
+        <v>-0.0525</v>
       </c>
       <c r="V2" t="n">
-        <v>2.041</v>
+        <v>-0.337</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7403</v>
+        <v>-0.337</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2666</v>
+        <v>4.2945</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6401</v>
+        <v>1.1176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6264999999999999</v>
+        <v>3.1769</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6929</v>
+        <v>2.5939</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8013</v>
+        <v>1.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.1084</v>
+        <v>1.498</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8558</v>
+        <v>1.554</v>
       </c>
       <c r="K3" t="n">
-        <v>6.0533</v>
+        <v>0.7466</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1975</v>
+        <v>0.8074</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1629</v>
+        <v>1.0399</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.252</v>
+        <v>0.3494</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9109</v>
+        <v>0.6905</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9822</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9196</v>
+        <v>0.0054</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1125</v>
+        <v>0.3387</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1929</v>
+        <v>-0.3333</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.337</v>
+        <v>1.1005</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.337</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1066</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5471</v>
+        <v>3.2787</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3421</v>
+        <v>1.4765</v>
       </c>
       <c r="F4" t="n">
-        <v>3.205</v>
+        <v>1.8022</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5939</v>
+        <v>-0.7464</v>
       </c>
       <c r="H4" t="n">
-        <v>1.096</v>
+        <v>-1.1673</v>
       </c>
       <c r="I4" t="n">
-        <v>1.498</v>
+        <v>0.421</v>
       </c>
       <c r="J4" t="n">
-        <v>1.554</v>
+        <v>1.286</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7466</v>
+        <v>-0.5777</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8074</v>
+        <v>1.8637</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0399</v>
+        <v>-2.0324</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3494</v>
+        <v>-0.5896</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6905</v>
+        <v>-1.4428</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5769</v>
+        <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.742</v>
+        <v>2.1823</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4368</v>
+        <v>1.4236</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3052</v>
+        <v>0.7587</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1005</v>
+        <v>2.041</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2071</v>
+        <v>1.7403</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1066</v>
+        <v>0.3008</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9491</v>
+        <v>2.8058</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7849</v>
+        <v>3.1924</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8358</v>
+        <v>-0.3866</v>
       </c>
       <c r="G5" t="n">
         <v>3.6488</v>
@@ -844,13 +844,13 @@
         <v>2.7751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7209</v>
+        <v>0.1358</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0696</v>
+        <v>0.3378</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6513</v>
+        <v>-0.202</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7806</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.898</v>
+        <v>1.159</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5477</v>
+        <v>-0.2586</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4457</v>
+        <v>1.4176</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0187</v>
@@ -1078,13 +1078,13 @@
         <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2904</v>
+        <v>-0.0294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2568</v>
+        <v>0.0322</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0335</v>
+        <v>-0.0616</v>
       </c>
       <c r="V8" t="n">
         <v>1.2071</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7316</v>
+        <v>1.1212</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4697</v>
+        <v>0.4857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2619</v>
+        <v>0.6355</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2175</v>
+        <v>0.643</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.093</v>
+        <v>1.6762</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1244</v>
+        <v>-1.0332</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1009</v>
+        <v>1.0762</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1009</v>
+        <v>1.5946</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5184</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3184</v>
+        <v>-0.4331</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1939</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1244</v>
+        <v>-0.5148</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3264</v>
+        <v>0.3955</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1138</v>
+        <v>0.1341</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2126</v>
+        <v>0.2614</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4737</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.9768</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7085</v>
+        <v>0.9635</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1572</v>
+        <v>0.6734</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5513</v>
+        <v>0.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.643</v>
+        <v>-0.2175</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6762</v>
+        <v>-0.093</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0332</v>
+        <v>-0.1244</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0762</v>
+        <v>0.1009</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5946</v>
+        <v>0.1009</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5184</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4331</v>
+        <v>-0.3184</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08160000000000001</v>
+        <v>-0.1939</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5148</v>
+        <v>-0.1244</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0173</v>
+        <v>-0.0945</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1944</v>
+        <v>0.09</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1772</v>
+        <v>-0.1845</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7102000000000001</v>
+        <v>1.4737</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>1.4737</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3659</v>
+        <v>-0.2016</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9049</v>
+        <v>-1.7406</v>
       </c>
       <c r="F12" t="n">
         <v>1.539</v>
@@ -1390,10 +1390,10 @@
         <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1762</v>
+        <v>0.3404</v>
       </c>
       <c r="T12" t="n">
-        <v>0.191</v>
+        <v>0.3553</v>
       </c>
       <c r="U12" t="n">
         <v>-0.0148</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7685</v>
+        <v>-0.4067</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0663</v>
+        <v>0.2393</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7022</v>
+        <v>-0.646</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2163</v>
@@ -1468,13 +1468,13 @@
         <v>0.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2856</v>
+        <v>0.0762</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1872</v>
+        <v>0.1184</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V13" t="n">
         <v>0.337</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.6196</v>
+        <v>-2.3585</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7216</v>
+        <v>1.1086</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.898</v>
+        <v>-3.4671</v>
       </c>
       <c r="G14" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.7323</v>
+      </c>
+      <c r="I14" t="n">
         <v>-1.6146</v>
       </c>
-      <c r="H14" t="n">
-        <v>-0.9469</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.6677</v>
-      </c>
       <c r="J14" t="n">
-        <v>-0.6791</v>
+        <v>2.0335</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6791</v>
+        <v>2.0581</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.0246</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9355</v>
+        <v>-1.9158</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2677</v>
+        <v>-0.3258</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6677</v>
+        <v>-1.59</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0139</v>
+        <v>0.0624</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0514</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0374</v>
+        <v>-0.0038</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-3.728</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-3.728</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.4106</v>
+        <v>-2.5635</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1688</v>
+        <v>-1.7216</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5794</v>
+        <v>-0.8419</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1177</v>
+        <v>-1.6146</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7323</v>
+        <v>-0.9469</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6146</v>
+        <v>-0.6677</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0335</v>
+        <v>-0.6791</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0581</v>
+        <v>-0.6791</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0246</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9158</v>
+        <v>-0.9355</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3258</v>
+        <v>-0.2677</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.59</v>
+        <v>-0.6677</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9897</v>
+        <v>0.0422</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8736</v>
+        <v>-0.0514</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1161</v>
+        <v>0.0936</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.728</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>15.2828</v>
+        <v>16.2188</v>
       </c>
       <c r="E16" t="n">
-        <v>10.9962</v>
+        <v>11.9323</v>
       </c>
       <c r="F16" t="n">
-        <v>4.286600000000002</v>
+        <v>4.286399999999998</v>
       </c>
       <c r="G16" t="n">
         <v>9.7788</v>
@@ -1702,16 +1702,16 @@
         <v>18.8311</v>
       </c>
       <c r="S16" t="n">
-        <v>2.918100000000001</v>
+        <v>3.854099999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6993</v>
+        <v>3.6352</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2188999999999999</v>
+        <v>0.219</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6035000000000008</v>
+        <v>0.6034999999999999</v>
       </c>
       <c r="W16" t="n">
         <v>6.961100000000001</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5629</v>
+        <v>3.4597</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7873</v>
+        <v>3.3798</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2244</v>
+        <v>0.0799</v>
       </c>
       <c r="G17" t="n">
         <v>1.1047</v>
@@ -1780,13 +1780,13 @@
         <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1666</v>
+        <v>-0.2698</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.213</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7871</v>
+        <v>-0.4828</v>
       </c>
       <c r="V17" t="n">
         <v>1.6336</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6781</v>
+        <v>1.129</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6355</v>
+        <v>2.9224</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9574</v>
+        <v>-1.7935</v>
       </c>
       <c r="G18" t="n">
         <v>0.1345</v>
@@ -1858,13 +1858,13 @@
         <v>2.9733</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1766</v>
+        <v>-0.3726</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7601</v>
+        <v>0.0471</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5835</v>
+        <v>-0.4196</v>
       </c>
       <c r="V18" t="n">
         <v>1.3671</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6747</v>
+        <v>0.4769</v>
       </c>
       <c r="E19" t="n">
-        <v>0.14</v>
+        <v>-0.1656</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5347</v>
+        <v>0.6425</v>
       </c>
       <c r="G19" t="n">
         <v>0.0988</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0.576</v>
+        <v>0.3781</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3782</v>
+        <v>0.0726</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1978</v>
+        <v>0.3055</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.1192</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9364</v>
+        <v>1.0382</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3855</v>
+        <v>-0.919</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2614</v>
@@ -2014,13 +2014,13 @@
         <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0994</v>
+        <v>-0.3322</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2861</v>
+        <v>-0.1843</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3855</v>
+        <v>-0.148</v>
       </c>
       <c r="V20" t="n">
         <v>2.3076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004</v>
+        <v>0.0285</v>
       </c>
       <c r="E21" t="n">
         <v>0.0512</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0508</v>
+        <v>-0.0227</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0917</v>
@@ -2092,13 +2092,13 @@
         <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1061</v>
+        <v>-0.078</v>
       </c>
       <c r="T21" t="n">
         <v>0.011</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0121</v>
+        <v>-1.1806</v>
       </c>
       <c r="E22" t="n">
         <v>-1.0576</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0455</v>
+        <v>-0.123</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1413</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1886</v>
+        <v>0.0202</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3758</v>
+        <v>0.2074</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2483</v>
+        <v>-2.294</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6038</v>
+        <v>-0.7057</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6445</v>
+        <v>-1.5883</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7153</v>
@@ -2248,13 +2248,13 @@
         <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2688</v>
+        <v>0.223</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3671</v>
+        <v>0.2653</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5712</v>
+        <v>-2.6485</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0335</v>
+        <v>-0.2185</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5377</v>
+        <v>-2.43</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7914</v>
@@ -2326,13 +2326,13 @@
         <v>3.3698</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6376</v>
+        <v>-0.7149</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1525</v>
+        <v>-0.3375</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4851</v>
+        <v>-0.3774</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5208</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7619</v>
+        <v>-3.8918</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7794</v>
+        <v>-2.8813</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-1.0105</v>
       </c>
       <c r="G25" t="n">
         <v>-2.898</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>0.264</v>
+        <v>0.134</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2423</v>
+        <v>0.1405</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0216</v>
+        <v>-0.0065</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5331</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.9753</v>
+        <v>-4.7376</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1234</v>
+        <v>-3.0215</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8519</v>
+        <v>-1.7161</v>
       </c>
       <c r="G26" t="n">
         <v>-1.5988</v>
@@ -2482,13 +2482,13 @@
         <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3854</v>
+        <v>-0.1477</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1176</v>
+        <v>0.2194</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.503</v>
+        <v>-0.3671</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2071</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.1809</v>
+        <v>-5.0642</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.239</v>
+        <v>-3.6278</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.9418</v>
+        <v>-1.4364</v>
       </c>
       <c r="G27" t="n">
         <v>-2.6187</v>
@@ -2560,13 +2560,13 @@
         <v>2.7751</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.1958</v>
+        <v>-1.0792</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.0901</v>
+        <v>-0.4788</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1058</v>
+        <v>-0.6004</v>
       </c>
       <c r="V27" t="n">
         <v>-0.177</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.2827</v>
+        <v>-14.6034</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.286300000000001</v>
+        <v>-4.2864</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.9962</v>
+        <v>-10.3171</v>
       </c>
       <c r="G28" t="n">
         <v>-9.778600000000001</v>
@@ -2638,13 +2638,13 @@
         <v>16.8487</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.9181</v>
+        <v>-2.2391</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.2191000000000001</v>
+        <v>-0.2189</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.6993</v>
+        <v>-2.0201</v>
       </c>
       <c r="V28" t="n">
         <v>-0.6033999999999999</v>
